--- a/gas/rsvp-sheet.xlsx
+++ b/gas/rsvp-sheet.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTA(RSVP!B2:B5000)</f>
+        <f>COUNTIF(RSVP!C2:C5000,"Hadir")+COUNTIF(RSVP!C2:C5000,"Tidak Hadir")</f>
         <v/>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Counts cover rows 2–5000 of the RSVP tab and update by themselves.</t>
+          <t>Counts cover rows 2–5000 of the RSVP tab and update by themselves. Guestbook-only messages (no attendance) count as wishes, not replies.</t>
         </is>
       </c>
     </row>
